--- a/test/fixtures/Test_format_bad_Seq.xlsx
+++ b/test/fixtures/Test_format_bad_Seq.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jc2017/Documents/MyRepos/safedata_validator/test/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379131E4-457F-3B45-A8ED-F2346D43F11C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3830178D-D4FD-2348-9DCE-6F7C8818B76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1060" windowWidth="27860" windowHeight="15840" activeTab="3" xr2:uid="{819B57D8-7F20-471A-9405-EB60A28E68AA}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8163" uniqueCount="1439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8165" uniqueCount="1442">
   <si>
     <t>Kingdom</t>
   </si>
@@ -4349,6 +4349,15 @@
   </si>
   <si>
     <t>carneum</t>
+  </si>
+  <si>
+    <t>test that blank works instead of NA</t>
+  </si>
+  <si>
+    <t>Just Eukaryote fine</t>
+  </si>
+  <si>
+    <t>Kingdom without superkingdom doesn't work</t>
   </si>
 </sst>
 </file>
@@ -6564,8 +6573,8 @@
       <c r="H7" t="s">
         <v>1414</v>
       </c>
-      <c r="I7" t="s">
-        <v>7</v>
+      <c r="J7" t="s">
+        <v>1439</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -6664,7 +6673,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>1379</v>
       </c>
@@ -6672,7 +6681,7 @@
         <v>1370</v>
       </c>
       <c r="C11" t="s">
-        <v>1384</v>
+        <v>7</v>
       </c>
       <c r="D11" t="s">
         <v>1386</v>
@@ -6692,14 +6701,16 @@
       <c r="I11" t="s">
         <v>1430</v>
       </c>
-      <c r="J11" s="1"/>
+      <c r="J11" s="1" t="s">
+        <v>1440</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>1380</v>
       </c>
       <c r="B12" t="s">
-        <v>1370</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
         <v>1384</v>
@@ -6721,6 +6732,9 @@
       </c>
       <c r="I12" t="s">
         <v>1436</v>
+      </c>
+      <c r="J12" t="s">
+        <v>1441</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">

--- a/test/fixtures/Test_format_bad_Seq.xlsx
+++ b/test/fixtures/Test_format_bad_Seq.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jc2017/Documents/MyRepos/safedata_validator/test/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3830178D-D4FD-2348-9DCE-6F7C8818B76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC068C3-E413-4246-9658-900970E87FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1060" windowWidth="27860" windowHeight="15840" activeTab="3" xr2:uid="{819B57D8-7F20-471A-9405-EB60A28E68AA}"/>
+    <workbookView xWindow="0" yWindow="1060" windowWidth="27860" windowHeight="15840" activeTab="4" xr2:uid="{819B57D8-7F20-471A-9405-EB60A28E68AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="6" r:id="rId1"/>
     <sheet name="Locations" sheetId="7" r:id="rId2"/>
     <sheet name="GBIFTaxa" sheetId="8" r:id="rId3"/>
     <sheet name="SeqTaxa" sheetId="1" r:id="rId4"/>
-    <sheet name="DF" sheetId="9" r:id="rId5"/>
-    <sheet name="Incidence" sheetId="10" r:id="rId6"/>
-    <sheet name="MicrobeDF" sheetId="11" r:id="rId7"/>
+    <sheet name="MoreTaxa" sheetId="12" r:id="rId5"/>
+    <sheet name="DF" sheetId="9" r:id="rId6"/>
+    <sheet name="Incidence" sheetId="10" r:id="rId7"/>
+    <sheet name="MicrobeDF" sheetId="11" r:id="rId8"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8165" uniqueCount="1442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8311" uniqueCount="1500">
   <si>
     <t>Kingdom</t>
   </si>
@@ -4358,6 +4359,180 @@
   </si>
   <si>
     <t>Kingdom without superkingdom doesn't work</t>
+  </si>
+  <si>
+    <t>Sequenced taxa sheet name</t>
+  </si>
+  <si>
+    <t>SeqTaxa</t>
+  </si>
+  <si>
+    <t>Reference database name</t>
+  </si>
+  <si>
+    <t>Greengenes</t>
+  </si>
+  <si>
+    <t>Reference database version</t>
+  </si>
+  <si>
+    <t>Reference database link</t>
+  </si>
+  <si>
+    <t>MoreTaxa</t>
+  </si>
+  <si>
+    <t>SILVA</t>
+  </si>
+  <si>
+    <t>v1.7.5</t>
+  </si>
+  <si>
+    <t>k__Fungi</t>
+  </si>
+  <si>
+    <t>p__Basidiomycota</t>
+  </si>
+  <si>
+    <t>c__Tremellomycetes</t>
+  </si>
+  <si>
+    <t>o__Tremellales</t>
+  </si>
+  <si>
+    <t>f__Trimorphomycetaceae</t>
+  </si>
+  <si>
+    <t>g__Saitozyma</t>
+  </si>
+  <si>
+    <t>s__podzolica</t>
+  </si>
+  <si>
+    <t>p__Ascomycota</t>
+  </si>
+  <si>
+    <t>c__Sordariomycetes</t>
+  </si>
+  <si>
+    <t>o__Hypocreales</t>
+  </si>
+  <si>
+    <t>f__Hypocreaceae</t>
+  </si>
+  <si>
+    <t>g__Trichoderma</t>
+  </si>
+  <si>
+    <t>s__spirale</t>
+  </si>
+  <si>
+    <t>o__Trichosporonales</t>
+  </si>
+  <si>
+    <t>f__Trichosporonaceae</t>
+  </si>
+  <si>
+    <t>g__Apiotrichum</t>
+  </si>
+  <si>
+    <t>s__sporotrichoides</t>
+  </si>
+  <si>
+    <t>p__Mortierellomycota</t>
+  </si>
+  <si>
+    <t>c__Mortierellomycetes</t>
+  </si>
+  <si>
+    <t>o__Mortierellales</t>
+  </si>
+  <si>
+    <t>f__Mortierellaceae</t>
+  </si>
+  <si>
+    <t>g__Mortierella</t>
+  </si>
+  <si>
+    <t>s__elongata</t>
+  </si>
+  <si>
+    <t>c__Eurotiomycetes</t>
+  </si>
+  <si>
+    <t>o__Eurotiales</t>
+  </si>
+  <si>
+    <t>f__Trichocomaceae</t>
+  </si>
+  <si>
+    <t>g__Talaromyces</t>
+  </si>
+  <si>
+    <t>f__Ophiocordycipitaceae</t>
+  </si>
+  <si>
+    <t>g__Purpureocillium</t>
+  </si>
+  <si>
+    <t>s__lilacinum</t>
+  </si>
+  <si>
+    <t>s__harzianum</t>
+  </si>
+  <si>
+    <t>c__Geoglossomycetes</t>
+  </si>
+  <si>
+    <t>o__Geoglossales</t>
+  </si>
+  <si>
+    <t>f__Geoglossaceae</t>
+  </si>
+  <si>
+    <t>g__Geoglossum</t>
+  </si>
+  <si>
+    <t>s__difforme</t>
+  </si>
+  <si>
+    <t>Example comment</t>
+  </si>
+  <si>
+    <t>c__Dothideomycetes</t>
+  </si>
+  <si>
+    <t>o__Pleosporales</t>
+  </si>
+  <si>
+    <t>f__Cucurbitariaceae</t>
+  </si>
+  <si>
+    <t>g__Pyrenochaetopsis</t>
+  </si>
+  <si>
+    <t>s__leptospora</t>
+  </si>
+  <si>
+    <t>s__koningiopsis</t>
+  </si>
+  <si>
+    <t>f__Clavicipitaceae</t>
+  </si>
+  <si>
+    <t>g__Metarhizium</t>
+  </si>
+  <si>
+    <t>s__carneum</t>
+  </si>
+  <si>
+    <t>o__Chaetosphaeriales</t>
+  </si>
+  <si>
+    <t>f__Chaetosphaeriaceae</t>
+  </si>
+  <si>
+    <t>g__Chloridium</t>
   </si>
 </sst>
 </file>
@@ -4745,7 +4920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{915E50AF-1B61-0E4A-B651-AEECBCF18168}">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
@@ -5020,6 +5195,45 @@
       <c r="B27">
         <v>5.07</v>
       </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B30">
+        <v>23</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B31" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6830,6 +7044,457 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F834ACA3-E463-3C4F-960F-80F4CCB849C2}">
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1460</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="I3" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1453</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1465</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1466</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1460</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1461</v>
+      </c>
+      <c r="H5" t="s">
+        <v>1462</v>
+      </c>
+      <c r="I5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1468</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1470</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1471</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1472</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1475</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1476</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1477</v>
+      </c>
+      <c r="I7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1460</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1461</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1462</v>
+      </c>
+      <c r="I9" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1483</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1484</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1485</v>
+      </c>
+      <c r="I10" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1460</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1461</v>
+      </c>
+      <c r="H11" t="s">
+        <v>1462</v>
+      </c>
+      <c r="I11" t="s">
+        <v>1481</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1489</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1490</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1491</v>
+      </c>
+      <c r="I12" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1460</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1461</v>
+      </c>
+      <c r="H13" t="s">
+        <v>1462</v>
+      </c>
+      <c r="I13" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1460</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1494</v>
+      </c>
+      <c r="H14" t="s">
+        <v>1495</v>
+      </c>
+      <c r="I14" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1498</v>
+      </c>
+      <c r="H15" t="s">
+        <v>1499</v>
+      </c>
+      <c r="I15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82695760-AFB9-9947-BCDE-2196089E5678}">
   <dimension ref="A1:U1038"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -70935,7 +71600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE462CF6-3A6E-774A-8E43-3D35D2607B6F}">
   <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -73739,7 +74404,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA3BCC54-7A77-6647-90D1-72E613354374}">
   <dimension ref="A1:N62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
